--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>25/07 01:10</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>27/07 17:15</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>45</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>22/07 22:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>27/07 13:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>60</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>22/07 18:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>55</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>22/07 16:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
+      <c r="F17" t="n">
+        <v>4.4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>25/07 19:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>25/07 16:45</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>24/07 18:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>27/07 17:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>45</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>22/07 18:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,97 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45860.0816983236</v>
+        <v>45860.08169832176</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | 1X | Aris Limas</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Aris Limassol – Puskas AcademyCoupes d'Europe - Europa Conference</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24/07 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>79,9%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+1,43%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45860.1536685907</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 21re période | Copenhague</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Copenhague – KF DritaEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21re période</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>16.50</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+1,26%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45860.1536685907</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>24/07 16:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
+      <c r="F27" t="n">
+        <v>1.27</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45860.1536685907</v>
+        <v>45860.15366858796</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
+      <c r="F28" t="n">
+        <v>16.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45860.1536685907</v>
+        <v>45860.15366858796</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Banfiel</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CA Banfield – Barracas CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>28/07 23:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+4,72%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45860.19540828507</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>45</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,52 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45860.19540828507</v>
+        <v>45860.19540828704</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FCSB – Far</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FCSB – Farul ConstantaLiga 1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>26/07 18:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+1,93%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45860.22775867039</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>40</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,277 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45860.22775867039</v>
+        <v>45860.22775866898</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Yannick Ha</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yannick Hanfmann – Lukas NeumayerATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>22/07 14:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+60,9%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45860.27469889154</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | D.Prizmic </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>D.Prizmic – E.MoellerATP - Umag</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>22/07 19:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+28,4%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45860.27469889154</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 7.5 - tir cadré | Corinthian</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Corinthians – CruzeiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>23/07 22:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>66,8%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+26,8%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45860.27469889154</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Vitoria BA – Sport RecifeBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>55,0%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+26,6%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45860.27469889154</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | Xin.Wang –</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Xin.Wang – H.DartWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>22/07 10:10</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+21,9%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45860.27469889154</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Fluminense</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fluminense – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>23/07 22:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>49,5%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45860.27469889154</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>22/07 14:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3.75</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45860.27469889154</v>
+        <v>45860.27469888889</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>22/07 19:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F32" t="n">
+        <v>1.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45860.27469889154</v>
+        <v>45860.27469888889</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>23/07 22:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F33" t="n">
+        <v>1.9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45860.27469889154</v>
+        <v>45860.27469888889</v>
       </c>
     </row>
     <row r="34">
@@ -1887,10 +1881,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1903,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45860.27469889154</v>
+        <v>45860.27469888889</v>
       </c>
     </row>
     <row r="35">
@@ -1932,10 +1924,8 @@
           <t>22/07 10:10</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1948,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45860.27469889154</v>
+        <v>45860.27469888889</v>
       </c>
     </row>
     <row r="36">
@@ -1977,10 +1967,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.4</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1993,7 +1981,142 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45860.27469889154</v>
+        <v>45860.27469888889</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré1re équipe | Fluminense</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fluminense – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>23/07 22:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>46,8%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+17,1%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45860.30948053112</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré1re équipe | Vasco de G</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Vasco de Gama – Independiente Del ValleInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23/07 00:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45860.30948053112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Angleterre – ItalieUEFA Euro (F) - Matchs</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>22/07 19:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+7,67%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45860.30948053112</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45860.30948053112</v>
+        <v>45860.30948053241</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>23/07 00:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45860.30948053112</v>
+        <v>45860.30948053241</v>
       </c>
     </row>
     <row r="39">
@@ -2100,23 +2096,66 @@
           <t>22/07 19:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>45</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+7,67%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45860.30948053241</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Hamrun Spa</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hamrun Spartans FC – Dynamo KievLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>+7,67%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>45860.30948053112</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+6,91%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45860.35622610615</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>45</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,187 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45860.35622610615</v>
+        <v>45860.35622611111</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tirs2e équipe | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lech Poznan – Breidablik KopavogurEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>22/07 18:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>54,2%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+11,1%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45860.3950576978</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs2e équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Angleterre F. – Italie F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>22/07 19:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+9,36%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45860.3950576978</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | David Goff</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>David Goffin – Yunchaokete BuATP - Washington</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22/07 15:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>66,1%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+5,84%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45860.3950576978</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 22.5 - tirs | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – PanathinaikosEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>22/07 18:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+5,46%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45860.3950576978</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>22/07 18:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.05</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45860.3950576978</v>
+        <v>45860.39505769676</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>22/07 19:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45860.3950576978</v>
+        <v>45860.39505769676</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>22/07 15:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F43" t="n">
+        <v>1.6</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45860.3950576978</v>
+        <v>45860.39505769676</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>22/07 18:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,97 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45860.3950576978</v>
+        <v>45860.39505769676</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lech Poznan – BreidablikLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>22/07 18:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+18,1%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45860.43541865991</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Thiago Sey</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Thiago Seyboth Wild – Justin EngelATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22/07 13:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>46,9%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+5,42%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45860.43541865991</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>22/07 18:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>55</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45860.43541865991</v>
+        <v>45860.43541865741</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>22/07 13:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.25</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,97 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45860.43541865991</v>
+        <v>45860.43541865741</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | B.Nakashim</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B.Nakashima – E.QuinnATP - Washington</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>22/07 15:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+9,47%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45860.47253353032</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Water-polo | Plus que 23.5 | Etats-Unis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Water-polo</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Etats-Unis – CroatieMonde - Mondial 2025 H</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 23.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>22/07 12:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>62,0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+6,55%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45860.47253353032</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>22/07 15:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.65</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45860.47253353032</v>
+        <v>45860.47253353009</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>22/07 12:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F48" t="n">
+        <v>1.72</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,142 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45860.47253353032</v>
+        <v>45860.47253353009</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 2.51re période1re équipe | Lincoln FC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lincoln FC – Étoile Rouge BelgradeEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re période1re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>22/07 16:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45860.53501293999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Vasco da G</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vasco da Gama – Independiente Del ValleCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>23/07 00:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+16,2%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45860.53501293999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 4.5 - aces | Dino Prizm</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dino Prizmic – Elmer MoellerATP - Umag</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>22/07 19:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45860.53501293999</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>22/07 16:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>100</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45860.53501293999</v>
+        <v>45860.53501293981</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>23/07 00:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>50</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45860.53501293999</v>
+        <v>45860.53501293981</v>
       </c>
     </row>
     <row r="51">
@@ -2616,10 +2612,8 @@
           <t>22/07 19:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.35</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2632,7 +2626,52 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45860.53501293999</v>
+        <v>45860.53501293981</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 2 | FC Riga – </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FC Riga – Metta/LuLettonie. Lettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>27/07 15:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+19,1%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45860.56956002257</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>27/07 15:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>30</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,52 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45860.56956002257</v>
+        <v>45860.56956002315</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Chicago Sk</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chicago Sky – Minnesota LynxUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>23/07 00:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>4,30%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+7,61%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45860.59945796553</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>23/07 00:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>25</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,142 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45860.59945796553</v>
+        <v>45860.59945796296</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Copenha</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FC Copenhague – KF DritaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,40%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+381%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45860.64372057669</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 24.5 - tirs | Angleterre</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Angleterre (F) – Italie (F)Europe - Euro (F)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>22/07 19:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>44,6%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+4,75%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45860.64372057669</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs1re équipe | Bragantino</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bragantino – FlamengoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>37,6%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+3,41%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45860.64372057669</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>200</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45860.64372057669</v>
+        <v>45860.6437205787</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>22/07 19:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.35</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45860.64372057669</v>
+        <v>45860.6437205787</v>
       </c>
     </row>
     <row r="56">
@@ -2831,10 +2827,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.75</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2847,7 +2841,97 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45860.64372057669</v>
+        <v>45860.6437205787</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Shanghai S</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua – Henan Songshan LongmenSuper League</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>27/07 11:35</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45860.68833548451</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Alexandre </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Alexandre Muller – Holger RuneATP - Washington</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>22/07 23:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>30,3%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+6,24%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45860.68833548451</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>27/07 11:35</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>50</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45860.68833548451</v>
+        <v>45860.68833548611</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>22/07 23:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F58" t="n">
+        <v>3.5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,52 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45860.68833548451</v>
+        <v>45860.68833548611</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | M.Kostyuk </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>M.Kostyuk – E.RaducanuWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>22/07 19:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+3,20%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45860.7245900046</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>22/07 19:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
+      <c r="F59" t="n">
+        <v>1.35</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,232 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45860.7245900046</v>
+        <v>45860.72459</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Lokomotiva</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb – HNK Vukovar 1991HNL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>01/08 18:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45860.77410895144</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 21-2- se qualifie | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – PanathinaïkosEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>22/07 18:45</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+5,43%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45860.77410895144</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Volleyball | H 1 (+1.5) | Pologne F </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Pologne F – Chine FMonde - Ligue des Nations F</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>H 1 (+1.5)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>23/07 18:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+3,07%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45860.77410895144</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Fluminense</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fluminense – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>23/07 22:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>36,7%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+2,63%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45860.77410895144</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Union Sant</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Union Santa Fe – CA TigreLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>26/07 00:15</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+2,24%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45860.77410895144</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45860.77410895144</v>
+        <v>45860.77410894676</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>22/07 18:45</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45860.77410895144</v>
+        <v>45860.77410894676</v>
       </c>
     </row>
     <row r="62">
@@ -3089,10 +3085,8 @@
           <t>23/07 18:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F62" t="n">
+        <v>1.6</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3105,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45860.77410895144</v>
+        <v>45860.77410894676</v>
       </c>
     </row>
     <row r="63">
@@ -3134,10 +3128,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2.8</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3150,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45860.77410895144</v>
+        <v>45860.77410894676</v>
       </c>
     </row>
     <row r="64">
@@ -3179,10 +3171,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>45</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3195,7 +3185,97 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45860.77410895144</v>
+        <v>45860.77410894676</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | X2 | Allemagne </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Allemagne F. – Espagne F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>23/07 19:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+0,97%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45860.80552213028</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Alex Miche</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Alex Michelsen – Daniel EvansATP - Washington</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>22/07 20:40</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>71,6%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+0,21%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45860.80552213028</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>23/07 19:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.17</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45860.80552213028</v>
+        <v>45860.80552212963</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>22/07 20:40</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="F66" t="n">
+        <v>1.4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,52 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45860.80552213028</v>
+        <v>45860.80552212963</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Jeonbuk Mo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors – Gangwon FCK League 1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>23/07 10:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45860.85190739318</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>23/07 10:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>45</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,187 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45860.85190739318</v>
+        <v>45860.85190739583</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Santa Fe –</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Santa Fe – Rionegro AguilasPrimera A</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>22/07 23:10</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+35,3%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45860.89084400898</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Atlanta Dr</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Atlanta Dream – Las Vegas AcesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>23/07 02:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+3,38%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45860.89084400898</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Ben Shelto</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ben Shelton – Mackenzie McDonaldATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>22/07 22:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+0,74%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45860.89084400898</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Tie-break: Oui | Arthur Rin</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech – Norbert GombosATP 250 Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>23/07 09:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+0,31%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45860.89084400898</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>22/07 23:10</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>60</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45860.89084400898</v>
+        <v>45860.89084400463</v>
       </c>
     </row>
     <row r="69">
@@ -3388,10 +3386,8 @@
           <t>23/07 02:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>25</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3404,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45860.89084400898</v>
+        <v>45860.89084400463</v>
       </c>
     </row>
     <row r="70">
@@ -3433,10 +3429,8 @@
           <t>22/07 22:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
+      <c r="F70" t="n">
+        <v>5.4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3449,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45860.89084400898</v>
+        <v>45860.89084400463</v>
       </c>
     </row>
     <row r="71">
@@ -3478,10 +3472,8 @@
           <t>23/07 09:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F71" t="n">
+        <v>2.45</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3494,7 +3486,142 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45860.89084400898</v>
+        <v>45860.89084400463</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>25/07 21:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+4,55%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45860.93265267678</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | La Equidad</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>La Equidad – Millonarios FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>24/07 01:20</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+4,37%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45860.93265267678</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X1re période[race to 15 regular time] | Atlanta Dr</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Atlanta Dream – Las Vegas AcesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>X1re période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>23/07 02:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+0,16%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45860.93265267678</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-22.xlsx
+++ b/data/valuebets_database_2025-07-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>25/07 21:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>40</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45860.93265267678</v>
+        <v>45860.93265267361</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>24/07 01:20</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>40</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45860.93265267678</v>
+        <v>45860.93265267361</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>23/07 02:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>40</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,52 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45860.93265267678</v>
+        <v>45860.93265267361</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Urawa Red </t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Urawa Red Diamonds – Shonan BellmareJ-League</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>23/07 10:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+5,47%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45860.97492468917</v>
       </c>
     </row>
   </sheetData>
